--- a/demo/reporte_analisis.xlsx
+++ b/demo/reporte_analisis.xlsx
@@ -59,7 +59,7 @@
     <t>Bajo meta</t>
   </si>
   <si>
-    <t>Luis MartÃ­nez</t>
+    <t>Luis Martínez</t>
   </si>
   <si>
     <t>Analytics Suite</t>
@@ -77,7 +77,7 @@
     <t>Centro</t>
   </si>
   <si>
-    <t>Pedro SÃ¡nchez</t>
+    <t>Pedro Sánchez</t>
   </si>
   <si>
     <t>CRM Pro</t>
@@ -101,7 +101,7 @@
     <t>Javier Castro</t>
   </si>
   <si>
-    <t>AndrÃ©s Reyes</t>
+    <t>Andrés Reyes</t>
   </si>
   <si>
     <t>Valentina Cruz</t>
@@ -161,10 +161,10 @@
     <t>%</t>
   </si>
   <si>
-    <t>Venta mÃ¡xima</t>
-  </si>
-  <si>
-    <t>Venta mÃ­nima</t>
+    <t>Venta máxima</t>
+  </si>
+  <si>
+    <t>Venta mínima</t>
   </si>
   <si>
     <t>Promedio por vendedor</t>
@@ -173,7 +173,7 @@
     <t>Mediana de ventas</t>
   </si>
   <si>
-    <t>DesviaciÃ³n estÃ¡ndar</t>
+    <t>Desviación estándar</t>
   </si>
   <si>
     <t>posicion</t>
@@ -182,10 +182,10 @@
     <t>Cumple</t>
   </si>
   <si>
-    <t>Elena DÃ­az</t>
-  </si>
-  <si>
-    <t>Francisco RÃ­os</t>
+    <t>Elena Díaz</t>
+  </si>
+  <si>
+    <t>Francisco Ríos</t>
   </si>
   <si>
     <t>Laura Vega</t>
@@ -194,13 +194,13 @@
     <t>Diego Herrera</t>
   </si>
   <si>
-    <t>Marta LÃ³pez</t>
-  </si>
-  <si>
-    <t>SofÃ­a Vargas</t>
-  </si>
-  <si>
-    <t>Ana GarcÃ­a</t>
+    <t>Marta López</t>
+  </si>
+  <si>
+    <t>Sofía Vargas</t>
+  </si>
+  <si>
+    <t>Ana García</t>
   </si>
   <si>
     <t>Carmen Medina</t>
@@ -209,7 +209,7 @@
     <t>Isabel Torres</t>
   </si>
   <si>
-    <t>HÃ©ctor Romero</t>
+    <t>Héctor Romero</t>
   </si>
 </sst>
 </file>
@@ -602,7 +602,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>88.57142857142857</v>
+        <v>88.6</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -640,7 +640,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>98.66666666666667</v>
+        <v>98.7</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -678,7 +678,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>84.61538461538461</v>
+        <v>84.6</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
@@ -716,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="B5">
-        <v>71.66666666666667</v>
+        <v>71.7</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -754,7 +754,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>95.71428571428571</v>
+        <v>95.7</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="B7">
-        <v>89.23076923076923</v>
+        <v>89.2</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="B8">
-        <v>89.0909090909091</v>
+        <v>89.1</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -868,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>92.6470588235294</v>
+        <v>92.6</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>70.6896551724138</v>
+        <v>70.7</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>103.99351073762838</v>
+        <v>104</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>96.75824175824175</v>
+        <v>96.75</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>101.7576407081051</v>
+        <v>101.775</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>106.7043332484509</v>
+        <v>106.70000000000002</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1269,7 +1269,7 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>100.2021563342318</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1324,7 +1324,7 @@
         <v>43</v>
       </c>
       <c r="C13">
-        <v>19095.221915442617</v>
+        <v>19095</v>
       </c>
     </row>
   </sheetData>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>122.22222222222223</v>
+        <v>122.2</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -1391,7 +1391,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>107.36842105263158</v>
+        <v>107.4</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
-        <v>109.0909090909091</v>
+        <v>109.1</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5">
-        <v>111.76470588235294</v>
+        <v>111.8</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
-        <v>107.05882352941177</v>
+        <v>107.1</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
-        <v>106.25</v>
+        <v>106.3</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>103.84615384615384</v>
+        <v>103.8</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
@@ -1599,7 +1599,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>106.94444444444444</v>
+        <v>106.9</v>
       </c>
       <c r="B11" t="s">
         <v>53</v>
